--- a/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 10,44</t>
+          <t>-6,28; 9,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,0</t>
+          <t>-4,53; 10,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 18,5</t>
+          <t>0,62; 16,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 3,81</t>
+          <t>-29,65; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 53,43</t>
+          <t>-22,8; 52,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 83,72</t>
+          <t>-25,28; 86,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 174,34</t>
+          <t>2,3; 149,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 29,17</t>
+          <t>-72,39; 21,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 11,08</t>
+          <t>-2,48; 11,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,99</t>
+          <t>-0,38; 11,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 8,0</t>
+          <t>-4,47; 7,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 13,4</t>
+          <t>-2,54; 13,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 53,57</t>
+          <t>-8,84; 54,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 94,98</t>
+          <t>-2,6; 90,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 47,05</t>
+          <t>-20,23; 47,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 95,86</t>
+          <t>-14,13; 102,11</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 10,83</t>
+          <t>-4,33; 9,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 10,77</t>
+          <t>-3,0; 11,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 13,02</t>
+          <t>-0,08; 13,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 37,91</t>
+          <t>-1,96; 36,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 68,35</t>
+          <t>-18,7; 61,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 71,48</t>
+          <t>-13,81; 77,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 105,76</t>
+          <t>-1,82; 106,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 229,02</t>
+          <t>-9,31; 203,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 4,85</t>
+          <t>-8,22; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 10,53</t>
+          <t>-1,37; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 11,37</t>
+          <t>-1,74; 11,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 12,73</t>
+          <t>-0,93; 12,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 21,97</t>
+          <t>-27,78; 24,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 89,61</t>
+          <t>-9,07; 91,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 81,57</t>
+          <t>-8,46; 81,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 127,98</t>
+          <t>-8,41; 116,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,31</t>
+          <t>-1,94; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,6</t>
+          <t>0,93; 7,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,27</t>
+          <t>1,64; 8,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 15,95</t>
+          <t>0,33; 17,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 24,81</t>
+          <t>-7,81; 25,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 53,47</t>
+          <t>5,04; 52,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 54,03</t>
+          <t>9,02; 58,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 101,24</t>
+          <t>0,54; 97,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,73</t>
+          <t>-6,14; 10,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 10,21</t>
+          <t>-4,66; 9,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 16,55</t>
+          <t>1,02; 16,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 2,62</t>
+          <t>-25,48; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 52,72</t>
+          <t>-22,36; 53,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 86,31</t>
+          <t>-24,54; 80,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 149,96</t>
+          <t>4,89; 162,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 21,0</t>
+          <t>-70,21; 25,93</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 11,04</t>
+          <t>-2,14; 11,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 11,88</t>
+          <t>-0,37; 12,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,39</t>
+          <t>-4,61; 7,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 13,69</t>
+          <t>-2,68; 13,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 54,94</t>
+          <t>-7,76; 55,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 90,01</t>
+          <t>-1,89; 91,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 47,19</t>
+          <t>-20,49; 46,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 102,11</t>
+          <t>-16,01; 98,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 9,94</t>
+          <t>-4,63; 10,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 11,35</t>
+          <t>-2,84; 11,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 13,1</t>
+          <t>-0,18; 12,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 36,84</t>
+          <t>-2,3; 41,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 61,81</t>
+          <t>-20,72; 61,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 77,36</t>
+          <t>-13,39; 77,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 106,01</t>
+          <t>0,03; 111,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 203,58</t>
+          <t>-11,15; 240,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 5,6</t>
+          <t>-8,22; 5,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,8</t>
+          <t>-1,68; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 11,43</t>
+          <t>-1,13; 10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,54</t>
+          <t>-1,32; 13,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 24,03</t>
+          <t>-27,68; 23,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 91,56</t>
+          <t>-10,21; 97,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 81,14</t>
+          <t>-5,85; 79,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 116,64</t>
+          <t>-9,31; 132,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,5</t>
+          <t>-1,79; 5,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,64</t>
+          <t>0,89; 8,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,55</t>
+          <t>1,71; 8,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 17,93</t>
+          <t>-0,38; 15,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 25,93</t>
+          <t>-7,38; 26,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 52,72</t>
+          <t>4,57; 57,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 58,78</t>
+          <t>8,73; 53,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 97,65</t>
+          <t>-2,37; 94,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,89</t>
+          <t>-6,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-28,55%</t>
+          <t>-31,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 10,13</t>
+          <t>-5,85; 10,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 9,81</t>
+          <t>-4,34; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 16,94</t>
+          <t>1,85; 18,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 3,34</t>
+          <t>-25,92; 2,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 53,41</t>
+          <t>-21,76; 53,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 80,38</t>
+          <t>-24,67; 83,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 162,54</t>
+          <t>9,68; 174,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 25,93</t>
+          <t>-76,95; 21,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 11,44</t>
+          <t>-2,6; 11,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 12,09</t>
+          <t>-0,63; 11,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 7,55</t>
+          <t>-3,99; 8,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 13,39</t>
+          <t>-2,37; 8,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 55,04</t>
+          <t>-9,54; 53,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 91,94</t>
+          <t>-2,71; 94,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 46,47</t>
+          <t>-17,91; 47,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 98,17</t>
+          <t>-14,6; 74,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 10,16</t>
+          <t>-4,76; 10,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,1</t>
+          <t>-3,06; 10,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 12,87</t>
+          <t>-0,37; 13,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 41,57</t>
+          <t>-5,81; 10,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 61,94</t>
+          <t>-19,82; 68,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 77,42</t>
+          <t>-17,02; 71,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 111,65</t>
+          <t>-2,6; 105,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 240,58</t>
+          <t>-22,89; 62,43</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 5,42</t>
+          <t>-8,67; 4,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 10,97</t>
+          <t>-2,27; 10,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 10,88</t>
+          <t>-1,64; 11,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 13,32</t>
+          <t>-3,23; 10,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 23,54</t>
+          <t>-29,8; 21,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 97,66</t>
+          <t>-12,36; 89,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 79,83</t>
+          <t>-8,32; 81,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 132,23</t>
+          <t>-18,93; 91,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,75</t>
+          <t>-1,94; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,03</t>
+          <t>1,23; 7,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,43</t>
+          <t>1,6; 8,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 15,96</t>
+          <t>-2,87; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 26,22</t>
+          <t>-7,92; 24,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 57,12</t>
+          <t>7,25; 53,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 53,99</t>
+          <t>9,06; 54,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 94,45</t>
+          <t>-15,86; 36,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-31,97%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.105180275881974</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.77351110544691</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.283983617153391</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.22563093273866</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.09125825432771573</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1804498150429411</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.6633993197995731</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3196832345846259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 10,44</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,34; 10,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 18,5</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-25,92; 2,64</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-21,76; 53,43</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-24,67; 83,72</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,68; 174,34</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-76,95; 21,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.848545964998638</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.340847353012518</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.850643610505879</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-25.92126778016786</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2176364460171338</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.246700059076115</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.09677095468886522</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7694507657180488</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.43966125435329</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.0047833382389</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>18.50167213005911</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.635673663534303</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5343439966994318</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.8372297855258227</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.743381919876238</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2149988093434947</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,6; 11,08</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 11,99</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 8,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 8,6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-9,54; 53,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 94,98</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-17,91; 47,05</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 74,21</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.341381691712201</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.825532680659162</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.778769943020186</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.0371628192785</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1853382040058325</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3676877471914409</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.09184164948096615</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.2202301035676387</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,43</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.59846187200238</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6276501716427128</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.986571621720639</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.365074015345003</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.09541738732708605</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02706046069781074</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1790793252333308</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1460357423799337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 10,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 10,77</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 13,02</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,81; 10,04</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-19,82; 68,35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-17,02; 71,48</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,6; 105,76</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-22,89; 62,43</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.08457685159945</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>11.992203727583</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.997763368852483</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.595863933372206</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5356626872594925</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9498109195775104</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4704752907181663</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7421099039775717</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,41</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,87</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.928227678696751</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.981071353176555</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.429586341281854</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.044375256143074</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1481675432900975</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2221834388393419</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4222525962372435</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.09734015628571156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,67; 4,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 10,53</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,64; 11,37</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,23; 10,02</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-29,8; 21,97</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-12,36; 89,61</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,32; 81,57</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,93; 91,23</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.756147577322063</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.06137288244076</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.3666692935979268</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.811345730768631</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1982173405046071</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1701611900955457</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.02604182992851974</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2289127365582012</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.83284269443507</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.76996825140391</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.02418925232095</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.03764043421581</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6835150045979286</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7147770380853534</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.057568761516939</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.6242505517432408</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.520279039215083</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.411552250186876</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.866988808475142</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.663567668784032</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.0578163587491619</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2967874564510787</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2816284657184515</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.265024650242569</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.673335992743453</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.271168411137231</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.635868061103798</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.234903975176242</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2980185249740471</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1235635123577853</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.0831630718497486</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1893046280742555</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.851324596367165</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.5278832486556</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>11.37359605420048</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.01643605684996</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2196868893702259</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8960866415224806</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8157237818000524</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9122737612029673</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,94; 5,31</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 7,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 8,27</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 5,35</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 24,81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 53,47</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 54,03</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-15,86; 36,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.88328907217443</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.383816075541716</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.158983543142718</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.318541741127788</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.08044540443068166</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2749764974685549</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.3071041157382747</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07970267222862448</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.941612367670936</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.228792136231546</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.600244214485234</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.865012993804087</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.07917703744726061</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.07247867375259745</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.09056376903349926</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1585717889975327</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.311134242741181</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.596844932496532</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.271142472386536</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.347693895098334</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2480542128992607</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5347135597567968</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5402743767416384</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3606103638541471</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
